--- a/Raw_Data/Elevation.xlsx
+++ b/Raw_Data/Elevation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\17034\Downloads\GSU PhD\Prof. Kirpich\Datasets\New datasets\Malaria\Final\Additional datasets\Covariates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\17034\Downloads\GSU PhD\Prof. Kirpich\Datasets\GitHub Files\Time-Series-Analysis-of-Malaria\Raw_Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8D67408-E444-4C5D-AC7B-4277E93A5213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A8A7263-246A-4DF5-93B0-7B9D6DD36DF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10760" yWindow="120" windowWidth="8320" windowHeight="10810" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1154,7 +1154,7 @@
         <v>52</v>
       </c>
       <c r="B2">
-        <v>1112</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -1162,7 +1162,7 @@
         <v>54</v>
       </c>
       <c r="B3">
-        <v>273</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -1170,7 +1170,7 @@
         <v>55</v>
       </c>
       <c r="B4">
-        <v>1013</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -1178,7 +1178,7 @@
         <v>56</v>
       </c>
       <c r="B5">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -1186,7 +1186,7 @@
         <v>51</v>
       </c>
       <c r="B6">
-        <v>1504</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
@@ -1194,7 +1194,7 @@
         <v>48</v>
       </c>
       <c r="B7">
-        <v>12</v>
+        <v>323</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -1202,7 +1202,7 @@
         <v>57</v>
       </c>
       <c r="B8">
-        <v>667</v>
+        <v>648</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
@@ -1210,7 +1210,7 @@
         <v>35</v>
       </c>
       <c r="B9">
-        <v>635</v>
+        <v>598</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
@@ -1218,7 +1218,7 @@
         <v>53</v>
       </c>
       <c r="B10">
-        <v>543</v>
+        <v>517</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
@@ -1226,7 +1226,7 @@
         <v>49</v>
       </c>
       <c r="B11">
-        <v>16</v>
+        <v>493</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
@@ -1234,7 +1234,7 @@
         <v>46</v>
       </c>
       <c r="B12">
-        <v>430</v>
+        <v>418</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
@@ -1242,7 +1242,7 @@
         <v>45</v>
       </c>
       <c r="B13">
-        <v>250</v>
+        <v>260</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
@@ -1250,7 +1250,7 @@
         <v>44</v>
       </c>
       <c r="B14">
-        <v>726</v>
+        <v>684</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
@@ -1258,7 +1258,7 @@
         <v>58</v>
       </c>
       <c r="B15">
-        <v>430</v>
+        <v>447</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
@@ -1266,7 +1266,7 @@
         <v>59</v>
       </c>
       <c r="B16">
-        <v>577</v>
+        <v>489</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
@@ -1274,7 +1274,7 @@
         <v>60</v>
       </c>
       <c r="B17">
-        <v>853</v>
+        <v>764</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
@@ -1282,7 +1282,7 @@
         <v>62</v>
       </c>
       <c r="B18">
-        <v>305</v>
+        <v>629</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
@@ -1290,7 +1290,7 @@
         <v>61</v>
       </c>
       <c r="B19">
-        <v>1330</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
@@ -1298,7 +1298,7 @@
         <v>63</v>
       </c>
       <c r="B20">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
@@ -1306,7 +1306,7 @@
         <v>64</v>
       </c>
       <c r="B21">
-        <v>34</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
@@ -1314,7 +1314,7 @@
         <v>65</v>
       </c>
       <c r="B22">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
@@ -1322,7 +1322,7 @@
         <v>66</v>
       </c>
       <c r="B23">
-        <v>472</v>
+        <v>441</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
@@ -1330,7 +1330,7 @@
         <v>67</v>
       </c>
       <c r="B24">
-        <v>70</v>
+        <v>34.799999999999997</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
@@ -1338,7 +1338,7 @@
         <v>68</v>
       </c>
       <c r="B25">
-        <v>762</v>
+        <v>785</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
@@ -1346,7 +1346,7 @@
         <v>69</v>
       </c>
       <c r="B26">
-        <v>243</v>
+        <v>215</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
@@ -1354,7 +1354,7 @@
         <v>70</v>
       </c>
       <c r="B27">
-        <v>615</v>
+        <v>542</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
@@ -1362,7 +1362,7 @@
         <v>71</v>
       </c>
       <c r="B28">
-        <v>779</v>
+        <v>946</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
@@ -1370,7 +1370,7 @@
         <v>72</v>
       </c>
       <c r="B29">
-        <v>343</v>
+        <v>318</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
@@ -1378,7 +1378,7 @@
         <v>73</v>
       </c>
       <c r="B30">
-        <v>276</v>
+        <v>260</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
@@ -1386,7 +1386,7 @@
         <v>74</v>
       </c>
       <c r="B31">
-        <v>345</v>
+        <v>354</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
@@ -1394,7 +1394,7 @@
         <v>75</v>
       </c>
       <c r="B32">
-        <v>1141</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
@@ -1402,7 +1402,7 @@
         <v>76</v>
       </c>
       <c r="B33">
-        <v>474</v>
+        <v>458</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
@@ -1410,7 +1410,7 @@
         <v>77</v>
       </c>
       <c r="B34">
-        <v>380</v>
+        <v>327</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
@@ -1418,7 +1418,7 @@
         <v>78</v>
       </c>
       <c r="B35">
-        <v>1598</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
@@ -1426,7 +1426,7 @@
         <v>43</v>
       </c>
       <c r="B36">
-        <v>6</v>
+        <v>349</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
@@ -1434,7 +1434,7 @@
         <v>79</v>
       </c>
       <c r="B37">
-        <v>69</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
@@ -1442,7 +1442,7 @@
         <v>80</v>
       </c>
       <c r="B38">
-        <v>279</v>
+        <v>197</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
@@ -1450,7 +1450,7 @@
         <v>81</v>
       </c>
       <c r="B39">
-        <v>410</v>
+        <v>419</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
@@ -1458,7 +1458,7 @@
         <v>82</v>
       </c>
       <c r="B40">
-        <v>1034</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
@@ -1466,7 +1466,7 @@
         <v>50</v>
       </c>
       <c r="B41">
-        <v>639</v>
+        <v>514</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
@@ -1474,7 +1474,7 @@
         <v>83</v>
       </c>
       <c r="B42">
-        <v>568</v>
+        <v>529</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
@@ -1490,7 +1490,7 @@
         <v>85</v>
       </c>
       <c r="B44">
-        <v>236</v>
+        <v>259</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
@@ -1498,7 +1498,7 @@
         <v>86</v>
       </c>
       <c r="B45">
-        <v>1100</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
@@ -1506,7 +1506,7 @@
         <v>87</v>
       </c>
       <c r="B46">
-        <v>1138</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
@@ -1514,7 +1514,7 @@
         <v>88</v>
       </c>
       <c r="B47">
-        <v>961</v>
+        <v>973</v>
       </c>
     </row>
   </sheetData>
